--- a/output/pdf_financials_xlsx/BYN.xlsx
+++ b/output/pdf_financials_xlsx/BYN.xlsx
@@ -861,10 +861,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.421062</v>
+        <v>-0.421062</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.000377427</v>
+        <v>-0.000377427</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>1.678823</v>
@@ -895,7 +895,7 @@
         <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>1.237023</v>
+        <v>-4.594669</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-3.687332</v>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.421062</v>
+        <v>-0.421062</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.000377427</v>
+        <v>-0.000377427</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>2.915846</v>
+        <v>-2.915846</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>-1.455024</v>
@@ -1085,13 +1085,13 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.421062</v>
+        <v>-0.421062</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.000377427</v>
+        <v>-0.000377427</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>2.915846</v>
+        <v>-2.915846</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>-1.455024</v>
@@ -1239,10 +1239,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.421062</v>
+        <v>-0.421062</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.000377427</v>
+        <v>-0.000377427</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>1.678823</v>
@@ -1295,10 +1295,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.421062</v>
+        <v>-0.421062</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.000377427</v>
+        <v>-0.000377427</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>1.678823</v>
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>73.68394404889617</v>
+        <v>273.6839440488961</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>165.1802529041691</v>
@@ -3881,7 +3881,7 @@
         <v>-1.455024</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>0.367909</v>
+        <v>-0.367909</v>
       </c>
       <c r="G99" s="3" t="n">
         <v>-4.282547</v>
@@ -7631,7 +7631,7 @@
         <v>-1.455024</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>0.367909</v>
+        <v>-0.367909</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -10797,10 +10797,10 @@
         </is>
       </c>
       <c r="G114" s="5" t="n">
-        <v>2.915846</v>
+        <v>-2.915846</v>
       </c>
       <c r="H114" s="5" t="n">
-        <v>1.455024</v>
+        <v>-1.455024</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
@@ -11044,10 +11044,10 @@
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>0.421062</v>
+        <v>-0.421062</v>
       </c>
       <c r="F119" s="5" t="n">
-        <v>0.000377427</v>
+        <v>-0.000377427</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/BYN.xlsx
+++ b/output/pdf_financials_xlsx/BYN.xlsx
@@ -749,10 +749,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.027421</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.019481</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -1239,10 +1239,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.421062</v>
+        <v>-0.448483</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.000377427</v>
+        <v>-0.019858427</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>1.678823</v>
@@ -1295,10 +1295,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.421062</v>
+        <v>-0.448483</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.000377427</v>
+        <v>-0.019858427</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>1.678823</v>
@@ -10987,7 +10987,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E118" s="5" t="n">

--- a/output/pdf_financials_xlsx/BYN.xlsx
+++ b/output/pdf_financials_xlsx/BYN.xlsx
@@ -898,10 +898,10 @@
         <v>-4.594669</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-3.687332</v>
+        <v>0.777284</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-1.356204</v>
+        <v>2.092022</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>2.793154</v>
@@ -1374,10 +1374,10 @@
         <v>273.6839440488961</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>165.1802529041691</v>
+        <v>34.81974709583086</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>78.66096943761806</v>
+        <v>121.3390305623819</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>-39.47529721790109</v>
@@ -4937,7 +4937,7 @@
         </is>
       </c>
       <c r="D132" s="3" t="n">
-        <v>9.738801</v>
+        <v>9.005364999999999</v>
       </c>
       <c r="E132" s="3" t="n">
         <v>-2.747127</v>
@@ -4969,7 +4969,7 @@
         </is>
       </c>
       <c r="D133" s="3" t="n">
-        <v>15.094844</v>
+        <v>14.361408</v>
       </c>
       <c r="E133" s="3" t="n">
         <v>11.614281</v>
@@ -5033,7 +5033,7 @@
         </is>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-0.395562</v>
+        <v>-1.128998</v>
       </c>
       <c r="E135" s="3" t="n">
         <v>-1.414292</v>
@@ -6485,7 +6485,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -7711,7 +7715,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
@@ -8915,7 +8923,11 @@
           <t>Net cash generated from (used in) operating activities</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
@@ -9936,7 +9948,11 @@
           <t>Interest revenue</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>-</t>
@@ -10432,7 +10448,11 @@
           <t>DEFERRED INCOME TAX RECOVERY (Note 9)</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
           <t>-</t>
@@ -10683,7 +10703,11 @@
           <t>Interest Revenue</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
           <t>-</t>
